--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1325,7 +1325,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1824,7 +1824,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -2083,7 +2083,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2700,7 +2700,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="80.703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9041" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9042" uniqueCount="761">
   <si>
     <t>Property</t>
   </si>
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -692,7 +692,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1099,7 +1099,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1151,7 +1151,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1328,7 +1328,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1357,7 +1357,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1718,7 +1718,10 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1748,7 +1751,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1785,7 +1788,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1860,7 +1863,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1895,7 +1898,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
@@ -1910,7 +1913,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1943,7 +1946,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -2676,15 +2679,15 @@
   <dimension ref="A1:AP235"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="75.43359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="55.65625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="64.671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.71484375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2695,28 +2698,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="80.703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.1875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19434,9 +19437,11 @@
       <c r="X139" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Y139" s="2"/>
+      <c r="Y139" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="Z139" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>83</v>
@@ -19472,27 +19477,27 @@
         <v>83</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19518,16 +19523,16 @@
         <v>211</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -19555,10 +19560,10 @@
         <v>346</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>83</v>
@@ -19576,7 +19581,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19597,10 +19602,10 @@
         <v>83</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>83</v>
@@ -19611,10 +19616,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19637,16 +19642,16 @@
         <v>83</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19696,7 +19701,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -19714,27 +19719,27 @@
         <v>83</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19757,16 +19762,16 @@
         <v>83</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19816,7 +19821,7 @@
         <v>83</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -19834,27 +19839,27 @@
         <v>83</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19877,19 +19882,19 @@
         <v>83</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>83</v>
@@ -19938,7 +19943,7 @@
         <v>83</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -19950,7 +19955,7 @@
         <v>83</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>83</v>
@@ -19959,10 +19964,10 @@
         <v>83</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>83</v>
@@ -19973,10 +19978,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20091,10 +20096,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20211,14 +20216,14 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -20240,10 +20245,10 @@
         <v>139</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>171</v>
@@ -20298,7 +20303,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20333,10 +20338,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20359,13 +20364,13 @@
         <v>83</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -20416,7 +20421,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -20425,7 +20430,7 @@
         <v>94</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>106</v>
@@ -20437,10 +20442,10 @@
         <v>83</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>83</v>
@@ -20451,10 +20456,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20477,13 +20482,13 @@
         <v>83</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20534,7 +20539,7 @@
         <v>83</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -20543,7 +20548,7 @@
         <v>94</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>106</v>
@@ -20555,10 +20560,10 @@
         <v>83</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>83</v>
@@ -20569,10 +20574,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20598,16 +20603,16 @@
         <v>211</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>83</v>
@@ -20635,10 +20640,10 @@
         <v>118</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>83</v>
@@ -20656,7 +20661,7 @@
         <v>83</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -20674,10 +20679,10 @@
         <v>83</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>433</v>
@@ -20691,10 +20696,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20720,16 +20725,16 @@
         <v>211</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>83</v>
@@ -20757,10 +20762,10 @@
         <v>346</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>83</v>
@@ -20778,7 +20783,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -20796,10 +20801,10 @@
         <v>83</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>433</v>
@@ -20813,10 +20818,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20839,17 +20844,17 @@
         <v>83</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>83</v>
@@ -20898,7 +20903,7 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -20922,7 +20927,7 @@
         <v>83</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>83</v>
@@ -20933,10 +20938,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20962,10 +20967,10 @@
         <v>228</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21016,7 +21021,7 @@
         <v>83</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -21037,10 +21042,10 @@
         <v>83</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>83</v>
@@ -21051,10 +21056,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21077,16 +21082,16 @@
         <v>95</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -21136,7 +21141,7 @@
         <v>83</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -21157,10 +21162,10 @@
         <v>83</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>83</v>
@@ -21171,10 +21176,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21197,16 +21202,16 @@
         <v>95</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -21256,7 +21261,7 @@
         <v>83</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -21277,10 +21282,10 @@
         <v>83</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>83</v>
@@ -21291,10 +21296,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21317,19 +21322,19 @@
         <v>95</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>83</v>
@@ -21378,7 +21383,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21399,10 +21404,10 @@
         <v>83</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>83</v>
@@ -21413,10 +21418,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21531,10 +21536,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21651,14 +21656,14 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21680,10 +21685,10 @@
         <v>139</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N158" t="s" s="2">
         <v>171</v>
@@ -21738,7 +21743,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -21773,10 +21778,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21802,13 +21807,13 @@
         <v>211</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O159" t="s" s="2">
         <v>344</v>
@@ -21840,7 +21845,7 @@
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>83</v>
@@ -21858,7 +21863,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>94</v>
@@ -21876,7 +21881,7 @@
         <v>83</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>351</v>
@@ -21893,10 +21898,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21922,13 +21927,13 @@
         <v>406</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O160" t="s" s="2">
         <v>409</v>
@@ -21980,7 +21985,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -21998,7 +22003,7 @@
         <v>83</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>412</v>
@@ -22015,10 +22020,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22044,13 +22049,13 @@
         <v>211</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="O161" t="s" s="2">
         <v>418</v>
@@ -22102,7 +22107,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -22137,10 +22142,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22166,16 +22171,16 @@
         <v>211</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>83</v>
@@ -22222,7 +22227,7 @@
         <v>143</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -22257,10 +22262,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>436</v>
@@ -22288,16 +22293,16 @@
         <v>211</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>83</v>
@@ -22346,7 +22351,7 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -22381,10 +22386,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22499,10 +22504,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22619,10 +22624,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22741,10 +22746,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22859,10 +22864,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22979,10 +22984,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23101,10 +23106,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23221,10 +23226,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23341,10 +23346,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23461,10 +23466,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23583,10 +23588,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23705,10 +23710,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C175" t="s" s="2">
         <v>465</v>
@@ -23736,16 +23741,16 @@
         <v>211</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>83</v>
@@ -23794,7 +23799,7 @@
         <v>83</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -23829,10 +23834,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23947,10 +23952,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24067,10 +24072,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24189,10 +24194,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24307,10 +24312,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24427,10 +24432,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24549,10 +24554,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24669,10 +24674,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24789,10 +24794,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24909,10 +24914,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25031,10 +25036,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25153,10 +25158,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C187" t="s" s="2">
         <v>480</v>
@@ -25184,16 +25189,16 @@
         <v>211</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>83</v>
@@ -25242,7 +25247,7 @@
         <v>83</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -25277,10 +25282,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25395,10 +25400,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25515,10 +25520,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25637,10 +25642,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25755,10 +25760,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25875,10 +25880,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25997,10 +26002,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26117,10 +26122,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26237,10 +26242,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26357,10 +26362,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26479,10 +26484,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26601,10 +26606,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C199" t="s" s="2">
         <v>495</v>
@@ -26632,16 +26637,16 @@
         <v>211</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>83</v>
@@ -26690,7 +26695,7 @@
         <v>83</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -26725,10 +26730,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26843,10 +26848,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26963,10 +26968,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27085,10 +27090,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27203,10 +27208,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27323,10 +27328,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27445,10 +27450,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27565,10 +27570,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27685,10 +27690,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27805,10 +27810,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27927,10 +27932,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28049,10 +28054,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C211" t="s" s="2">
         <v>510</v>
@@ -28080,16 +28085,16 @@
         <v>211</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>83</v>
@@ -28138,7 +28143,7 @@
         <v>83</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
@@ -28173,10 +28178,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28291,10 +28296,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28411,10 +28416,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28533,10 +28538,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28651,10 +28656,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28771,10 +28776,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28893,10 +28898,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29013,10 +29018,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29133,10 +29138,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29253,10 +29258,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29375,10 +29380,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29497,10 +29502,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C223" t="s" s="2">
         <v>525</v>
@@ -29528,16 +29533,16 @@
         <v>211</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O223" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>83</v>
@@ -29586,7 +29591,7 @@
         <v>83</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -29621,10 +29626,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29739,10 +29744,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29859,10 +29864,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29981,10 +29986,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30099,10 +30104,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30219,10 +30224,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30341,10 +30346,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30461,10 +30466,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30581,10 +30586,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30701,10 +30706,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30823,10 +30828,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30945,10 +30950,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30974,16 +30979,16 @@
         <v>84</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="O235" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>83</v>
@@ -31032,7 +31037,7 @@
         <v>83</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
@@ -31053,10 +31058,10 @@
         <v>83</v>
       </c>
       <c r="AM235" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN235" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO235" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
